--- a/results/09-2025/beta/contributions-09-2025.xlsx
+++ b/results/09-2025/beta/contributions-09-2025.xlsx
@@ -20371,7 +20371,7 @@
         <v>0.0509724224221796</v>
       </c>
       <c r="H203" t="n">
-        <v>0.013024842362121</v>
+        <v>0.0130709783914536</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -20428,19 +20428,19 @@
         <v>-2.40291806709527</v>
       </c>
       <c r="AA203" t="n">
-        <v>0.224367436632777</v>
+        <v>0.224413412368527</v>
       </c>
       <c r="AB203" t="n">
         <v>8.7402010647946</v>
       </c>
       <c r="AC203" t="n">
-        <v>8.93149922495679</v>
+        <v>8.93153842042054</v>
       </c>
       <c r="AD203" t="n">
-        <v>10.3609808636547</v>
+        <v>10.3610200591185</v>
       </c>
       <c r="AE203" t="n">
-        <v>3.0076921202683</v>
+        <v>3.00770191913424</v>
       </c>
     </row>
     <row r="204">
@@ -20466,7 +20466,7 @@
         <v>0.0882420963372026</v>
       </c>
       <c r="H204" t="n">
-        <v>0.0150494420365095</v>
+        <v>0.0142536607940294</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -20523,19 +20523,19 @@
         <v>-0.0777936433941105</v>
       </c>
       <c r="AA204" t="n">
-        <v>0.578665060276391</v>
+        <v>0.577872790035862</v>
       </c>
       <c r="AB204" t="n">
         <v>5.13318105464696</v>
       </c>
       <c r="AC204" t="n">
-        <v>5.68843796299973</v>
+        <v>5.68767776557707</v>
       </c>
       <c r="AD204" t="n">
-        <v>3.96270746584012</v>
+        <v>3.96194726841747</v>
       </c>
       <c r="AE204" t="n">
-        <v>3.82868674178683</v>
+        <v>3.8285064912971</v>
       </c>
     </row>
     <row r="205">
@@ -20561,7 +20561,7 @@
         <v>-0.176051206004369</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0114473399759692</v>
+        <v>0.0113226472344793</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -20618,19 +20618,19 @@
         <v>0.0545355776769774</v>
       </c>
       <c r="AA205" t="n">
-        <v>-0.550485059451652</v>
+        <v>-0.55061048311181</v>
       </c>
       <c r="AB205" t="n">
         <v>-2.37437618060059</v>
       </c>
       <c r="AC205" t="n">
-        <v>-2.93843816613688</v>
+        <v>-2.93856668022048</v>
       </c>
       <c r="AD205" t="n">
-        <v>-3.22605477074292</v>
+        <v>-3.22618328482652</v>
       </c>
       <c r="AE205" t="n">
-        <v>2.89175827762405</v>
+        <v>2.89154589861342</v>
       </c>
     </row>
     <row r="206">
@@ -20656,7 +20656,7 @@
         <v>0.0432338115668846</v>
       </c>
       <c r="H206" t="n">
-        <v>-0.0143954679691977</v>
+        <v>-0.0209979545035528</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -20713,19 +20713,19 @@
         <v>-0.578067763509771</v>
       </c>
       <c r="AA206" t="n">
-        <v>-0.184640239222943</v>
+        <v>-0.191253752313974</v>
       </c>
       <c r="AB206" t="n">
         <v>7.92470585706429</v>
       </c>
       <c r="AC206" t="n">
-        <v>7.75461674113653</v>
+        <v>7.74852426728156</v>
       </c>
       <c r="AD206" t="n">
-        <v>8.52349989785585</v>
+        <v>8.51740742400088</v>
       </c>
       <c r="AE206" t="n">
-        <v>4.90528336415195</v>
+        <v>4.90354786667758</v>
       </c>
     </row>
     <row r="207">
@@ -20751,7 +20751,7 @@
         <v>0.0163838656257723</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.0380075901064802</v>
+        <v>-0.04099516736765</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -20808,19 +20808,19 @@
         <v>-0.922068055946882</v>
       </c>
       <c r="AA207" t="n">
-        <v>-0.248492651285064</v>
+        <v>-0.251485979135565</v>
       </c>
       <c r="AB207" t="n">
         <v>-1.00760734891081</v>
       </c>
       <c r="AC207" t="n">
-        <v>-1.25838712508508</v>
+        <v>-1.2614079929296</v>
       </c>
       <c r="AD207" t="n">
-        <v>-2.46721769239003</v>
+        <v>-2.47023856023454</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.69823372514076</v>
+        <v>1.69573321183932</v>
       </c>
     </row>
     <row r="208">
@@ -20846,7 +20846,7 @@
         <v>0.0270885464711389</v>
       </c>
       <c r="H208" t="n">
-        <v>-0.0427787314310142</v>
+        <v>-0.0400490243288701</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -20903,19 +20903,19 @@
         <v>-0.288955015927002</v>
       </c>
       <c r="AA208" t="n">
-        <v>-0.32449270025953</v>
+        <v>-0.321755275129595</v>
       </c>
       <c r="AB208" t="n">
         <v>-2.04938525022606</v>
       </c>
       <c r="AC208" t="n">
-        <v>-2.38053295664563</v>
+        <v>-2.37773942014669</v>
       </c>
       <c r="AD208" t="n">
-        <v>-3.27518504188077</v>
+        <v>-3.27239150538183</v>
       </c>
       <c r="AE208" t="n">
-        <v>-0.111239401789466</v>
+        <v>-0.112851481610505</v>
       </c>
     </row>
     <row r="209">
@@ -20941,7 +20941,7 @@
         <v>0.0595933393769765</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.0479898797029148</v>
+        <v>-0.0381545853545693</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -20998,19 +20998,19 @@
         <v>-0.719107012904098</v>
       </c>
       <c r="AA209" t="n">
-        <v>-0.226076491037271</v>
+        <v>-0.216223891057639</v>
       </c>
       <c r="AB209" t="n">
         <v>-2.39975636363618</v>
       </c>
       <c r="AC209" t="n">
-        <v>-2.63117510944837</v>
+        <v>-2.62108977304644</v>
       </c>
       <c r="AD209" t="n">
-        <v>-3.01081245918058</v>
+        <v>-3.00072712277864</v>
       </c>
       <c r="AE209" t="n">
-        <v>-0.0574288238988813</v>
+        <v>-0.0564874410985353</v>
       </c>
     </row>
     <row r="210">
@@ -21036,7 +21036,7 @@
         <v>-0.0673753500629978</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.0644326247869448</v>
+        <v>-0.0614188517797346</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -21093,19 +21093,19 @@
         <v>-0.578494355599297</v>
       </c>
       <c r="AA210" t="n">
-        <v>-0.901954333577364</v>
+        <v>-0.898914797558318</v>
       </c>
       <c r="AB210" t="n">
         <v>-2.1376509743099</v>
       </c>
       <c r="AC210" t="n">
-        <v>-3.05922857041098</v>
+        <v>-3.05612300629043</v>
       </c>
       <c r="AD210" t="n">
-        <v>-3.95144389138139</v>
+        <v>-3.94833832726084</v>
       </c>
       <c r="AE210" t="n">
-        <v>-3.17616477120819</v>
+        <v>-3.17292387891396</v>
       </c>
     </row>
     <row r="211">
@@ -21131,7 +21131,7 @@
         <v>-0.226525357084815</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.0813646603670895</v>
+        <v>-0.0766419470170181</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -21188,19 +21188,19 @@
         <v>-1.01817197043943</v>
       </c>
       <c r="AA211" t="n">
-        <v>-1.24102284066391</v>
+        <v>-1.23624585600344</v>
       </c>
       <c r="AB211" t="n">
         <v>-3.07974183533128</v>
       </c>
       <c r="AC211" t="n">
-        <v>-4.35848327384657</v>
+        <v>-4.35356139840116</v>
       </c>
       <c r="AD211" t="n">
-        <v>-4.98810879964595</v>
+        <v>-4.98318692420053</v>
       </c>
       <c r="AE211" t="n">
-        <v>-3.80638754802217</v>
+        <v>-3.80116096990546</v>
       </c>
     </row>
     <row r="212">
@@ -21226,7 +21226,7 @@
         <v>0.0352466536178089</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.0815149548087399</v>
+        <v>-0.0737260045796243</v>
       </c>
       <c r="I212" t="n">
         <v>0.0769149503246465</v>
@@ -21283,19 +21283,19 @@
         <v>0.502787293499322</v>
       </c>
       <c r="AA212" t="n">
-        <v>-0.623860061675733</v>
+        <v>-0.616027573782073</v>
       </c>
       <c r="AB212" t="n">
         <v>-1.68071578105547</v>
       </c>
       <c r="AC212" t="n">
-        <v>-2.31536191685408</v>
+        <v>-2.30739415464263</v>
       </c>
       <c r="AD212" t="n">
-        <v>-2.4037480514443</v>
+        <v>-2.39578028923286</v>
       </c>
       <c r="AE212" t="n">
-        <v>-3.58852830041305</v>
+        <v>-3.58200816586822</v>
       </c>
     </row>
     <row r="213">
@@ -21321,7 +21321,7 @@
         <v>0.122322426031235</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.0677195935663334</v>
+        <v>-0.0614819118189263</v>
       </c>
       <c r="I213" t="n">
         <v>0.0498106688116675</v>
@@ -21378,19 +21378,19 @@
         <v>0.571714489003667</v>
       </c>
       <c r="AA213" t="n">
-        <v>-0.330514986725024</v>
+        <v>-0.324260090310348</v>
       </c>
       <c r="AB213" t="n">
         <v>-0.406199500910894</v>
       </c>
       <c r="AC213" t="n">
-        <v>-0.73812453965835</v>
+        <v>-0.731842973572884</v>
       </c>
       <c r="AD213" t="n">
-        <v>-0.408421414624425</v>
+        <v>-0.402139848538958</v>
       </c>
       <c r="AE213" t="n">
-        <v>-2.93793053927401</v>
+        <v>-2.9323613473083</v>
       </c>
     </row>
     <row r="214">
@@ -21416,7 +21416,7 @@
         <v>0.121967585304644</v>
       </c>
       <c r="H214" t="n">
-        <v>-0.0888831324672848</v>
+        <v>-0.0972572991622061</v>
       </c>
       <c r="I214" t="n">
         <v>0.352811260215887</v>
@@ -21473,19 +21473,19 @@
         <v>0.357776493404253</v>
       </c>
       <c r="AA214" t="n">
-        <v>0.75704425233315</v>
+        <v>0.748742442276019</v>
       </c>
       <c r="AB214" t="n">
         <v>-1.19014757636623</v>
       </c>
       <c r="AC214" t="n">
-        <v>-0.423909010324724</v>
+        <v>-0.432311775937189</v>
       </c>
       <c r="AD214" t="n">
-        <v>-0.096302440741205</v>
+        <v>-0.10470520635367</v>
       </c>
       <c r="AE214" t="n">
-        <v>-1.97414517661397</v>
+        <v>-1.9714530670815</v>
       </c>
     </row>
     <row r="215">
@@ -21511,7 +21511,7 @@
         <v>0.186037345056342</v>
       </c>
       <c r="H215" t="n">
-        <v>-0.0821940867312759</v>
+        <v>-0.0894936530882256</v>
       </c>
       <c r="I215" t="n">
         <v>0.235358292343292</v>
@@ -21568,19 +21568,19 @@
         <v>0.414469238862886</v>
       </c>
       <c r="AA215" t="n">
-        <v>0.698554529700505</v>
+        <v>0.691315172812197</v>
       </c>
       <c r="AB215" t="n">
         <v>-1.32629278524743</v>
       </c>
       <c r="AC215" t="n">
-        <v>-0.617962806040482</v>
+        <v>-0.625303593945089</v>
       </c>
       <c r="AD215" t="n">
-        <v>-0.436629078407267</v>
+        <v>-0.443969866311874</v>
       </c>
       <c r="AE215" t="n">
-        <v>-0.836275246304299</v>
+        <v>-0.836648802609339</v>
       </c>
     </row>
     <row r="216">
@@ -21606,7 +21606,7 @@
         <v>0.0977160489726682</v>
       </c>
       <c r="H216" t="n">
-        <v>-0.0591532101359378</v>
+        <v>-0.0706901136249193</v>
       </c>
       <c r="I216" t="n">
         <v>0.23102780499548</v>
@@ -21663,19 +21663,19 @@
         <v>0.63724132469916</v>
       </c>
       <c r="AA216" t="n">
-        <v>0.349324044384497</v>
+        <v>0.337836298969782</v>
       </c>
       <c r="AB216" t="n">
         <v>-0.734196597892148</v>
       </c>
       <c r="AC216" t="n">
-        <v>-0.382198635228767</v>
+        <v>-0.393774366123229</v>
       </c>
       <c r="AD216" t="n">
-        <v>0.116699512414719</v>
+        <v>0.105123781520258</v>
       </c>
       <c r="AE216" t="n">
-        <v>-0.206163355339544</v>
+        <v>-0.211422784921061</v>
       </c>
     </row>
     <row r="217">
@@ -21701,7 +21701,7 @@
         <v>0.0520442383727039</v>
       </c>
       <c r="H217" t="n">
-        <v>-0.0716999059054796</v>
+        <v>-0.0824607733990141</v>
       </c>
       <c r="I217" t="n">
         <v>0.082750407381656</v>
@@ -21758,19 +21758,19 @@
         <v>0.123075625809095</v>
       </c>
       <c r="AA217" t="n">
-        <v>0.109920446431576</v>
+        <v>0.0991802501470916</v>
       </c>
       <c r="AB217" t="n">
         <v>-0.719347477899018</v>
       </c>
       <c r="AC217" t="n">
-        <v>-0.608591014769169</v>
+        <v>-0.619412911595139</v>
       </c>
       <c r="AD217" t="n">
-        <v>-0.203618350008679</v>
+        <v>-0.214440246834649</v>
       </c>
       <c r="AE217" t="n">
-        <v>-0.154962589185608</v>
+        <v>-0.164497884494983</v>
       </c>
     </row>
     <row r="218">
@@ -21796,7 +21796,7 @@
         <v>0.208391135077172</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.0603919336737449</v>
+        <v>-0.049307544114358</v>
       </c>
       <c r="I218" t="n">
         <v>0.127323007835629</v>
@@ -21853,19 +21853,19 @@
         <v>0.143271512428738</v>
       </c>
       <c r="AA218" t="n">
-        <v>0.732678477725149</v>
+        <v>0.743670148290004</v>
       </c>
       <c r="AB218" t="n">
         <v>-0.507684037215612</v>
       </c>
       <c r="AC218" t="n">
-        <v>0.228917102365608</v>
+        <v>0.239967698450387</v>
       </c>
       <c r="AD218" t="n">
-        <v>0.230201053166659</v>
+        <v>0.241251649251438</v>
       </c>
       <c r="AE218" t="n">
-        <v>-0.0733367157086416</v>
+        <v>-0.0780086705937065</v>
       </c>
     </row>
     <row r="219">
@@ -21891,7 +21891,7 @@
         <v>0.181328332896499</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.0469193767608715</v>
+        <v>-0.0437184319785973</v>
       </c>
       <c r="I219" t="n">
         <v>0.0945287269652199</v>
@@ -21948,19 +21948,19 @@
         <v>-0.0169547352652505</v>
       </c>
       <c r="AA219" t="n">
-        <v>0.555864153602898</v>
+        <v>0.559045043511163</v>
       </c>
       <c r="AB219" t="n">
         <v>-0.435603111701512</v>
       </c>
       <c r="AC219" t="n">
-        <v>0.122777318364768</v>
+        <v>0.125972621508951</v>
       </c>
       <c r="AD219" t="n">
-        <v>0.29765454470428</v>
+        <v>0.300849847848463</v>
       </c>
       <c r="AE219" t="n">
-        <v>0.110234190069245</v>
+        <v>0.108196257946378</v>
       </c>
     </row>
     <row r="220">
@@ -21986,7 +21986,7 @@
         <v>0.0214977195653354</v>
       </c>
       <c r="H220" t="n">
-        <v>-0.0437030238309972</v>
+        <v>-0.0469048133827945</v>
       </c>
       <c r="I220" t="n">
         <v>-0.0953655996897482</v>
@@ -22043,19 +22043,19 @@
         <v>-0.092578391855672</v>
       </c>
       <c r="AA220" t="n">
-        <v>0.13795910196057</v>
+        <v>0.134763398238193</v>
       </c>
       <c r="AB220" t="n">
         <v>-0.0354056046573151</v>
       </c>
       <c r="AC220" t="n">
-        <v>0.102604629247405</v>
+        <v>0.0994077408188973</v>
       </c>
       <c r="AD220" t="n">
-        <v>0.645802031392392</v>
+        <v>0.642605142963884</v>
       </c>
       <c r="AE220" t="n">
-        <v>0.242509819813663</v>
+        <v>0.242566598307284</v>
       </c>
     </row>
     <row r="221">
@@ -22081,7 +22081,7 @@
         <v>0.0290948586183631</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.0343392663544733</v>
+        <v>-0.0435950185239223</v>
       </c>
       <c r="I221" t="n">
         <v>-0.133729009875071</v>
@@ -22138,19 +22138,19 @@
         <v>0.0221654378119154</v>
       </c>
       <c r="AA221" t="n">
-        <v>0.13854798222895</v>
+        <v>0.129308826051373</v>
       </c>
       <c r="AB221" t="n">
         <v>0.232705671663</v>
       </c>
       <c r="AC221" t="n">
-        <v>0.37091899841144</v>
+        <v>0.361702163928976</v>
       </c>
       <c r="AD221" t="n">
-        <v>0.54563281254695</v>
+        <v>0.536415978064486</v>
       </c>
       <c r="AE221" t="n">
-        <v>0.429822610452571</v>
+        <v>0.430280654532068</v>
       </c>
     </row>
     <row r="222">
@@ -22176,7 +22176,7 @@
         <v>0.0458242790354847</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.00426482013373204</v>
+        <v>-0.0298993084457546</v>
       </c>
       <c r="I222" t="n">
         <v>0.0248512999833828</v>
@@ -22233,19 +22233,19 @@
         <v>0.614168817041161</v>
       </c>
       <c r="AA222" t="n">
-        <v>0.0111027166496448</v>
+        <v>-0.0145276111562999</v>
       </c>
       <c r="AB222" t="n">
         <v>0.0255255934034087</v>
       </c>
       <c r="AC222" t="n">
-        <v>0.0366253165184027</v>
+        <v>0.011001899031202</v>
       </c>
       <c r="AD222" t="n">
-        <v>-0.51915719448429</v>
+        <v>-0.544780611971491</v>
       </c>
       <c r="AE222" t="n">
-        <v>0.242483048539833</v>
+        <v>0.233772589226336</v>
       </c>
     </row>
     <row r="223">
@@ -22271,7 +22271,7 @@
         <v>-0.0393319122031674</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00705799436909313</v>
+        <v>-0.0250922849159152</v>
       </c>
       <c r="I223" t="n">
         <v>0.187169199391747</v>
@@ -22328,19 +22328,19 @@
         <v>0.539879048845966</v>
       </c>
       <c r="AA223" t="n">
-        <v>-0.335911181138249</v>
+        <v>-0.36817689423191</v>
       </c>
       <c r="AB223" t="n">
         <v>0.445302181314265</v>
       </c>
       <c r="AC223" t="n">
-        <v>-0.189041894533449</v>
+        <v>-0.221157176688978</v>
       </c>
       <c r="AD223" t="n">
-        <v>-0.595126013032959</v>
+        <v>-0.627241295188488</v>
       </c>
       <c r="AE223" t="n">
-        <v>0.0192879091055238</v>
+        <v>0.00174980346709823</v>
       </c>
     </row>
     <row r="224">
@@ -22354,88 +22354,88 @@
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.0292183114064904</v>
+        <v>0.163111297253933</v>
       </c>
       <c r="E224" t="n">
         <v>-0.188957509209438</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.3254684597094</v>
+        <v>-0.225617648258191</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.00232627880914326</v>
+        <v>0.0319644152423085</v>
       </c>
       <c r="H224" t="n">
-        <v>0.181388548391829</v>
+        <v>0.180032319887456</v>
       </c>
       <c r="I224" t="n">
-        <v>0.184098990026918</v>
+        <v>0.18199766032276</v>
       </c>
       <c r="J224" t="n">
-        <v>0.00533005884222482</v>
+        <v>0.0069886573575032</v>
       </c>
       <c r="K224" t="n">
-        <v>0.325604907806274</v>
+        <v>0.237483789099726</v>
       </c>
       <c r="L224" t="n">
-        <v>0.00415082726682935</v>
+        <v>-0.000244094540940933</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>-0.000993887583434497</v>
+        <v>-0.000998960935110496</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.007566531995738</v>
+        <v>-0.00836737074601288</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.0733093825076561</v>
+        <v>-0.0746265037458759</v>
       </c>
       <c r="R224" t="n">
-        <v>-0.0259828066413223</v>
+        <v>-0.0260482060281687</v>
       </c>
       <c r="S224" t="n">
-        <v>-0.013690159906531</v>
+        <v>-0.0138103838239934</v>
       </c>
       <c r="T224" t="n">
-        <v>-0.00846676495233506</v>
+        <v>-0.00854233864330229</v>
       </c>
       <c r="U224" t="n">
-        <v>-0.0295822537247447</v>
+        <v>-0.0296383233628748</v>
       </c>
       <c r="V224" t="n">
-        <v>-0.000519051526507596</v>
+        <v>-0.00052655433301353</v>
       </c>
       <c r="W224" t="n">
-        <v>0.250871602848468</v>
+        <v>0.224500594225563</v>
       </c>
       <c r="X224" t="n">
-        <v>0.00272592475901042</v>
+        <v>0.0019343238159437</v>
       </c>
       <c r="Y224" t="n">
-        <v>-0.0231109036108688</v>
+        <v>0.110782082236574</v>
       </c>
       <c r="Z224" t="n">
         <v>-0.136628294192079</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.0439249210999017</v>
+        <v>0.175822943742496</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.423225967989083</v>
+        <v>0.301240157261443</v>
       </c>
       <c r="AC224" t="n">
-        <v>0.166954185270714</v>
+        <v>0.176502666106995</v>
       </c>
       <c r="AD224" t="n">
-        <v>0.00721498746776617</v>
+        <v>0.150656454151489</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.140358851875633</v>
+        <v>-0.121237368736</v>
       </c>
     </row>
     <row r="225">
@@ -22449,19 +22449,19 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.474186700000211</v>
+        <v>0.0512774270456173</v>
       </c>
       <c r="E225" t="n">
         <v>-0.187978569902349</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.217103417495115</v>
+        <v>-0.183764822990767</v>
       </c>
       <c r="G225" t="n">
         <v>0.0128550363366188</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0659420428142137</v>
+        <v>0.0613252075112202</v>
       </c>
       <c r="I225" t="n">
         <v>0.0710975321691573</v>
@@ -22470,7 +22470,7 @@
         <v>0.00969819542473578</v>
       </c>
       <c r="K225" t="n">
-        <v>0.192448818987443</v>
+        <v>0.15390502911734</v>
       </c>
       <c r="L225" t="n">
         <v>0.0268155371055342</v>
@@ -22506,31 +22506,31 @@
         <v>-0.000445468017451337</v>
       </c>
       <c r="W225" t="n">
-        <v>0.217348161272175</v>
+        <v>0.229470804287544</v>
       </c>
       <c r="X225" t="n">
-        <v>0.0142456685546658</v>
+        <v>0.0201526179780047</v>
       </c>
       <c r="Y225" t="n">
-        <v>-0.578536131290393</v>
+        <v>-0.0530720042445649</v>
       </c>
       <c r="Z225" t="n">
         <v>-0.0836291386121668</v>
       </c>
       <c r="AA225" t="n">
-        <v>-0.0572275871317332</v>
+        <v>-0.028566525642904</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.356190350489848</v>
+        <v>0.335710507253734</v>
       </c>
       <c r="AC225" t="n">
-        <v>-0.000821228810473029</v>
+        <v>0.00724560892498743</v>
       </c>
       <c r="AD225" t="n">
-        <v>-0.662986498713033</v>
+        <v>-0.129455533931744</v>
       </c>
       <c r="AE225" t="n">
-        <v>-0.442513679690628</v>
+        <v>-0.287705246735058</v>
       </c>
     </row>
     <row r="226">
@@ -22544,19 +22544,19 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.0514292419304881</v>
+        <v>0.295885049451618</v>
       </c>
       <c r="E226" t="n">
         <v>-0.186793267437541</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.174114275163233</v>
+        <v>-0.157889086807043</v>
       </c>
       <c r="G226" t="n">
         <v>-0.00517525296486206</v>
       </c>
       <c r="H226" t="n">
-        <v>0.063538307727449</v>
+        <v>0.0710651834633598</v>
       </c>
       <c r="I226" t="n">
         <v>0.313882330011445</v>
@@ -22565,7 +22565,7 @@
         <v>0.00650702053184741</v>
       </c>
       <c r="K226" t="n">
-        <v>0.0692355173588614</v>
+        <v>0.0306232180642184</v>
       </c>
       <c r="L226" t="n">
         <v>0.0406439380982409</v>
@@ -22601,31 +22601,31 @@
         <v>-0.000411448413644342</v>
       </c>
       <c r="W226" t="n">
-        <v>0.261001777140825</v>
+        <v>0.273004908836868</v>
       </c>
       <c r="X226" t="n">
-        <v>0.0234807882795888</v>
+        <v>0.0293317054991943</v>
       </c>
       <c r="Y226" t="n">
-        <v>-0.000270140391721768</v>
+        <v>0.244185667129409</v>
       </c>
       <c r="Z226" t="n">
         <v>-0.135093885115331</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.205121909729358</v>
+        <v>0.228796037006046</v>
       </c>
       <c r="AB226" t="n">
-        <v>0.336044394476696</v>
+        <v>0.315373329348911</v>
       </c>
       <c r="AC226" t="n">
-        <v>0.240432802368097</v>
+        <v>0.303401530744063</v>
       </c>
       <c r="AD226" t="n">
-        <v>0.105068776861043</v>
+        <v>0.41249331275814</v>
       </c>
       <c r="AE226" t="n">
-        <v>-0.286457186854295</v>
+        <v>-0.0483867655526503</v>
       </c>
     </row>
     <row r="227">
@@ -22639,19 +22639,19 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.0207371589313447</v>
+        <v>0.0250630313682093</v>
       </c>
       <c r="E227" t="n">
         <v>-0.197884698811488</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.124832326051577</v>
+        <v>-0.108594546287687</v>
       </c>
       <c r="G227" t="n">
         <v>0.00260357465574721</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0611998687653726</v>
+        <v>0.0680470636217771</v>
       </c>
       <c r="I227" t="n">
         <v>0.248836761092057</v>
@@ -22660,7 +22660,7 @@
         <v>0.0044335969424576</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.165504056406091</v>
+        <v>-0.203501351198498</v>
       </c>
       <c r="L227" t="n">
         <v>0.0494236866899661</v>
@@ -22696,31 +22696,31 @@
         <v>-0.000382465757702634</v>
       </c>
       <c r="W227" t="n">
-        <v>0.174635472424906</v>
+        <v>0.186608335863096</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0258374923643587</v>
+        <v>0.0316397620714538</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.10501824540976</v>
+        <v>-0.0592180551102062</v>
       </c>
       <c r="Z227" t="n">
         <v>-0.113603612333072</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.19247657796431</v>
+        <v>0.215496172883615</v>
       </c>
       <c r="AB227" t="n">
-        <v>0.0370550767568108</v>
+        <v>0.0169377412432056</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.0294558906177271</v>
+        <v>0.0923951406086339</v>
       </c>
       <c r="AD227" t="n">
-        <v>-0.189165967125105</v>
+        <v>-0.0804265268346446</v>
       </c>
       <c r="AE227" t="n">
-        <v>-0.184967175377332</v>
+        <v>0.0883169265358106</v>
       </c>
     </row>
     <row r="228">
@@ -22734,19 +22734,19 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.0672338735788414</v>
+        <v>-0.0394192773292133</v>
       </c>
       <c r="E228" t="n">
         <v>-0.187670702662083</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.123084400281957</v>
+        <v>-0.107081655066805</v>
       </c>
       <c r="G228" t="n">
         <v>0.0154957709249802</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0662902833135336</v>
+        <v>0.0771097637552797</v>
       </c>
       <c r="I228" t="n">
         <v>0.0765546489014246</v>
@@ -22755,7 +22755,7 @@
         <v>0.00372772927577937</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.0756383898692935</v>
+        <v>-0.0748441661112643</v>
       </c>
       <c r="L228" t="n">
         <v>0.00936757390650711</v>
@@ -22791,31 +22791,31 @@
         <v>-0.000332772769679777</v>
       </c>
       <c r="W228" t="n">
-        <v>0.169820981246569</v>
+        <v>0.169949150288061</v>
       </c>
       <c r="X228" t="n">
-        <v>0.00565084088782152</v>
+        <v>0.00568467963863912</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.101183457770621</v>
+        <v>-0.073368861520993</v>
       </c>
       <c r="Z228" t="n">
         <v>-0.153721118470303</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.0391127766981881</v>
+        <v>0.0659086274037584</v>
       </c>
       <c r="AB228" t="n">
-        <v>0.0686275844093696</v>
+        <v>0.0695827083430077</v>
       </c>
       <c r="AC228" t="n">
-        <v>-0.0922883002304809</v>
+        <v>-0.00455763583675278</v>
       </c>
       <c r="AD228" t="n">
-        <v>-0.347192876471405</v>
+        <v>-0.231647615828049</v>
       </c>
       <c r="AE228" t="n">
-        <v>-0.273569141362125</v>
+        <v>-0.007259090959074</v>
       </c>
     </row>
     <row r="229">
@@ -22829,19 +22829,19 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.161943202133455</v>
+        <v>-0.134754265364598</v>
       </c>
       <c r="E229" t="n">
         <v>-0.198482369960888</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.101240625624439</v>
+        <v>-0.0853676104400794</v>
       </c>
       <c r="G229" t="n">
         <v>0.0267850730649783</v>
       </c>
       <c r="H229" t="n">
-        <v>0.0723467298766376</v>
+        <v>0.0823875929231884</v>
       </c>
       <c r="I229" t="n">
         <v>-0.0532196303747984</v>
@@ -22850,7 +22850,7 @@
         <v>0.0054605074072783</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.0277355659423336</v>
+        <v>-0.0269397539141716</v>
       </c>
       <c r="L229" t="n">
         <v>0.00948248106826557</v>
@@ -22886,31 +22886,31 @@
         <v>-0.000327314952247994</v>
       </c>
       <c r="W229" t="n">
-        <v>0.115820354782222</v>
+        <v>0.115959358088856</v>
       </c>
       <c r="X229" t="n">
-        <v>-0.00717227480414963</v>
+        <v>-0.00711132425766731</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.220731882879527</v>
+        <v>-0.19354294611067</v>
       </c>
       <c r="Z229" t="n">
         <v>-0.139693689214816</v>
       </c>
       <c r="AA229" t="n">
-        <v>-0.0497796645015467</v>
+        <v>-0.0238631014631728</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.0683172236140219</v>
+        <v>0.0693121952895956</v>
       </c>
       <c r="AC229" t="n">
-        <v>-0.181426223598347</v>
+        <v>-0.0945332908330871</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.54185179569269</v>
+        <v>-0.427769926158573</v>
       </c>
       <c r="AE229" t="n">
-        <v>-0.243285465607039</v>
+        <v>-0.0818376890157812</v>
       </c>
     </row>
     <row r="230">
@@ -22924,19 +22924,19 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.159255093872876</v>
+        <v>-0.0640674773934715</v>
       </c>
       <c r="E230" t="n">
         <v>-0.202712782891321</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.210352068691114</v>
+        <v>-0.194568075207978</v>
       </c>
       <c r="G230" t="n">
         <v>0.0180376150833894</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0797772531471791</v>
+        <v>0.074983445819594</v>
       </c>
       <c r="I230" t="n">
         <v>-0.200247462482823</v>
@@ -22945,7 +22945,7 @@
         <v>0.00553307401008943</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.0124822484633467</v>
+        <v>-0.0117522773604514</v>
       </c>
       <c r="L230" t="n">
         <v>0.0103984789268344</v>
@@ -22981,31 +22981,31 @@
         <v>-0.000320879541638737</v>
       </c>
       <c r="W230" t="n">
-        <v>0.107078470768821</v>
+        <v>0.107258849208799</v>
       </c>
       <c r="X230" t="n">
-        <v>-0.0040155315197057</v>
+        <v>-0.00393618236598118</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.20401638387948</v>
+        <v>-0.108828767400076</v>
       </c>
       <c r="Z230" t="n">
         <v>-0.157951492884716</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.307268848444784</v>
+        <v>-0.296281379518062</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.0858319512043388</v>
+        <v>0.0868208496266219</v>
       </c>
       <c r="AC230" t="n">
-        <v>-0.321156574117391</v>
+        <v>-0.24918711070573</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.683124450881588</v>
+        <v>-0.515967370990522</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.440333772542697</v>
+        <v>-0.313952859952947</v>
       </c>
     </row>
     <row r="231">
@@ -23019,19 +23019,19 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.137330321232357</v>
+        <v>-0.110727166879507</v>
       </c>
       <c r="E231" t="n">
         <v>-0.19118455586668</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0453855544405396</v>
+        <v>-0.0298367603268296</v>
       </c>
       <c r="G231" t="n">
         <v>0.0238002829895917</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0885153834975229</v>
+        <v>0.0882326187914347</v>
       </c>
       <c r="I231" t="n">
         <v>-0.311151219316299</v>
@@ -23040,7 +23040,7 @@
         <v>0.00463048903581738</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.0080950601480784</v>
+        <v>-0.0073764977580548</v>
       </c>
       <c r="L231" t="n">
         <v>0.0106138953337674</v>
@@ -23076,31 +23076,31 @@
         <v>-0.00031358356411215</v>
       </c>
       <c r="W231" t="n">
-        <v>0.088978719417739</v>
+        <v>0.0891696556739792</v>
       </c>
       <c r="X231" t="n">
-        <v>0.00121408745979923</v>
+        <v>0.00132367143557229</v>
       </c>
       <c r="Y231" t="n">
-        <v>-0.18116967516642</v>
+        <v>-0.15456652081357</v>
       </c>
       <c r="Z231" t="n">
         <v>-0.147345201932617</v>
       </c>
       <c r="AA231" t="n">
-        <v>-0.239324197016392</v>
+        <v>-0.224026936191922</v>
       </c>
       <c r="AB231" t="n">
-        <v>0.0817534527541221</v>
+        <v>0.0827717637621858</v>
       </c>
       <c r="AC231" t="n">
-        <v>-0.257361839565957</v>
+        <v>-0.181057179117255</v>
       </c>
       <c r="AD231" t="n">
-        <v>-0.585876716664993</v>
+        <v>-0.482968901863442</v>
       </c>
       <c r="AE231" t="n">
-        <v>-0.539511459927669</v>
+        <v>-0.414588453710146</v>
       </c>
     </row>
     <row r="232">
@@ -23114,19 +23114,19 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>-6.41118928522798</v>
+        <v>-6.65602787308324</v>
       </c>
       <c r="E232" t="n">
         <v>-10.9420859482975</v>
       </c>
       <c r="F232" t="n">
-        <v>7.75100144575484</v>
+        <v>7.7199969775895</v>
       </c>
       <c r="G232" t="n">
         <v>3.97895902244593</v>
       </c>
       <c r="H232" t="n">
-        <v>0.222277633409587</v>
+        <v>0.223827062650306</v>
       </c>
       <c r="I232" t="n">
         <v>-1.56547117640625</v>
@@ -23135,7 +23135,7 @@
         <v>0.0800378665131831</v>
       </c>
       <c r="K232" t="n">
-        <v>-7.52431397601782</v>
+        <v>-7.48236896993747</v>
       </c>
       <c r="L232" t="n">
         <v>-0.684161506988033</v>
@@ -23171,31 +23171,31 @@
         <v>-0.000248650698717219</v>
       </c>
       <c r="W232" t="n">
-        <v>-6.20959509923755</v>
+        <v>-6.22284987928125</v>
       </c>
       <c r="X232" t="n">
-        <v>-1.02253975079654</v>
+        <v>-1.0286535197463</v>
       </c>
       <c r="Y232" t="n">
-        <v>-7.97116680841173</v>
+        <v>-8.21600539626698</v>
       </c>
       <c r="Z232" t="n">
         <v>-9.38210842511378</v>
       </c>
       <c r="AA232" t="n">
-        <v>10.2910815116967</v>
+        <v>10.2624078357611</v>
       </c>
       <c r="AB232" t="n">
-        <v>-16.3584491380162</v>
+        <v>-16.3345994897278</v>
       </c>
       <c r="AC232" t="n">
-        <v>-4.27941352229038</v>
+        <v>-4.29186327795017</v>
       </c>
       <c r="AD232" t="n">
-        <v>-21.6326887558159</v>
+        <v>-21.8899770993309</v>
       </c>
       <c r="AE232" t="n">
-        <v>-5.86088542976379</v>
+        <v>-5.82917082458587</v>
       </c>
     </row>
     <row r="233">
@@ -23215,13 +23215,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F233" t="n">
-        <v>7.70142362162316</v>
+        <v>7.67080150880787</v>
       </c>
       <c r="G233" t="n">
         <v>3.94590494334522</v>
       </c>
       <c r="H233" t="n">
-        <v>0.225831086649703</v>
+        <v>0.227767131683752</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -23230,7 +23230,7 @@
         <v>0.0803545817220195</v>
       </c>
       <c r="K233" t="n">
-        <v>-7.41501753397275</v>
+        <v>-7.37385752289481</v>
       </c>
       <c r="L233" t="n">
         <v>-0.681523518982172</v>
@@ -23266,10 +23266,10 @@
         <v>-0.000244292150727557</v>
       </c>
       <c r="W233" t="n">
-        <v>-6.15278059005326</v>
+        <v>-6.16598967860645</v>
       </c>
       <c r="X233" t="n">
-        <v>-1.00142663357373</v>
+        <v>-1.00751433276352</v>
       </c>
       <c r="Y233" t="e">
         <v>#NUM!</v>
@@ -23278,19 +23278,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA233" t="n">
-        <v>11.5840582677893</v>
+        <v>11.5565693553665</v>
       </c>
       <c r="AB233" t="n">
-        <v>-16.1200892767043</v>
+        <v>-16.0970219687368</v>
       </c>
       <c r="AC233" t="n">
-        <v>-2.5489710599517</v>
+        <v>-2.56099332997049</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.72542248084062</v>
+        <v>-5.72222834304622</v>
       </c>
     </row>
     <row r="234">
@@ -23310,13 +23310,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>3.87231896030399</v>
+        <v>3.85641785240184</v>
       </c>
       <c r="G234" t="n">
         <v>1.98156625001828</v>
       </c>
       <c r="H234" t="n">
-        <v>0.20566840374926</v>
+        <v>0.22678795872225</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>0.0830797180841042</v>
       </c>
       <c r="K234" t="n">
-        <v>-7.44225595223442</v>
+        <v>-7.40093146648055</v>
       </c>
       <c r="L234" t="n">
         <v>-0.678495617656775</v>
@@ -23361,10 +23361,10 @@
         <v>-0.000239831117060016</v>
       </c>
       <c r="W234" t="n">
-        <v>-6.12867759340005</v>
+        <v>-6.14183398592377</v>
       </c>
       <c r="X234" t="n">
-        <v>-0.997409765184548</v>
+        <v>-1.00347289042589</v>
       </c>
       <c r="Y234" t="e">
         <v>#NUM!</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>6.04174848306974</v>
+        <v>6.04602842615194</v>
       </c>
       <c r="AB234" t="n">
-        <v>-16.1075971436</v>
+        <v>-16.0842843907452</v>
       </c>
       <c r="AC234" t="n">
-        <v>-9.04287447259915</v>
+        <v>-9.01599422425598</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.55464136812022</v>
+        <v>-5.59323650029859</v>
       </c>
     </row>
     <row r="235">
@@ -23405,13 +23405,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.82702813639797</v>
+        <v>3.81129213333326</v>
       </c>
       <c r="G235" t="n">
         <v>1.96075414671372</v>
       </c>
       <c r="H235" t="n">
-        <v>0.201864242876775</v>
+        <v>0.227331337387597</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>0.080910769730396</v>
       </c>
       <c r="K235" t="n">
-        <v>-7.34102041698405</v>
+        <v>-7.30055443249846</v>
       </c>
       <c r="L235" t="n">
         <v>-0.674501723777255</v>
@@ -23456,10 +23456,10 @@
         <v>-0.000235086391430304</v>
       </c>
       <c r="W235" t="n">
-        <v>-6.09597824595896</v>
+        <v>-6.1090638692887</v>
       </c>
       <c r="X235" t="n">
-        <v>-0.991926347790894</v>
+        <v>-0.997955996922773</v>
       </c>
       <c r="Y235" t="e">
         <v>#NUM!</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.97198778032943</v>
+        <v>5.98051515976208</v>
       </c>
       <c r="AB235" t="n">
-        <v>-15.9451202030495</v>
+        <v>-15.9226137363114</v>
       </c>
       <c r="AC235" t="n">
-        <v>-8.97108241119169</v>
+        <v>-8.9399831716845</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>-5.40817218895397</v>
+        <v>-5.47249427483273</v>
       </c>
     </row>
     <row r="236">
@@ -23500,7 +23500,7 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.78985415947378</v>
+        <v>3.77425017861906</v>
       </c>
       <c r="G236" t="n">
         <v>1.94233922292806</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.76632936958317</v>
+        <v>5.75107431919078</v>
       </c>
       <c r="AB236" t="n">
         <v>-0.0791194075164663</v>
       </c>
       <c r="AC236" t="n">
-        <v>5.69212635000089</v>
+        <v>5.67685815187102</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -23595,7 +23595,7 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.748984534156</v>
+        <v>3.73352820826225</v>
       </c>
       <c r="G237" t="n">
         <v>1.92321107800067</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.80100666372605</v>
+        <v>5.78590884834594</v>
       </c>
       <c r="AB237" t="n">
         <v>-0.0658847382059019</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.73923915859185</v>
+        <v>5.72413051056499</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -23690,7 +23690,7 @@
         <v>#NUM!</v>
       </c>
       <c r="F238" t="n">
-        <v>3.78350004839511</v>
+        <v>3.76819108188613</v>
       </c>
       <c r="G238" t="n">
         <v>1.9064840467514</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>5.81444521609934</v>
+        <v>5.79948734979815</v>
       </c>
       <c r="AB238" t="n">
         <v>-0.0665611196593151</v>
       </c>
       <c r="AC238" t="n">
-        <v>5.75204752879209</v>
+        <v>5.737078834794</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -23785,7 +23785,7 @@
         <v>#NUM!</v>
       </c>
       <c r="F239" t="n">
-        <v>3.73588428945396</v>
+        <v>3.72071616589733</v>
       </c>
       <c r="G239" t="n">
         <v>1.88728653658363</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>5.74522819967062</v>
+        <v>5.73040367231711</v>
       </c>
       <c r="AB239" t="n">
         <v>-0.0638434127351031</v>
       </c>
       <c r="AC239" t="n">
-        <v>5.68532676396352</v>
+        <v>5.67049195533087</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -23955,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -24050,7 +24050,7 @@
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -24145,7 +24145,7 @@
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -24335,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -24430,7 +24430,7 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -24525,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
